--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -35,7 +35,7 @@
     <t>编号【KEY】</t>
   </si>
   <si>
-    <t>角色id</t>
+    <t>皮肤id</t>
   </si>
   <si>
     <t>名称</t>
@@ -58,7 +58,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>roleId</t>
+    <t>skinId</t>
   </si>
   <si>
     <t>name</t>
@@ -1343,7 +1343,6 @@
       <c r="E12" s="1">
         <v>3</v>
       </c>
-      <c r="F12" s="1"/>
       <c r="G12" s="1">
         <v>10</v>
       </c>
@@ -1377,7 +1376,6 @@
       <c r="E14" s="1">
         <v>3</v>
       </c>
-      <c r="F14" s="1"/>
       <c r="G14" s="1">
         <v>20</v>
       </c>

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -107,15 +107,6 @@
   </si>
   <si>
     <t>角色7</t>
-  </si>
-  <si>
-    <t>角色8</t>
-  </si>
-  <si>
-    <t>角色9</t>
-  </si>
-  <si>
-    <t>角色10</t>
   </si>
 </sst>
 </file>
@@ -1348,52 +1339,22 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="4">
-        <v>8</v>
-      </c>
-      <c r="B13" s="4">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="1">
-        <v>2</v>
-      </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="4">
-        <v>9</v>
-      </c>
-      <c r="B14" s="4">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="1">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1">
-        <v>20</v>
-      </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="4">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4"/>

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -88,25 +88,25 @@
     <t>client</t>
   </si>
   <si>
-    <t>角色1</t>
+    <t>躺平宅男</t>
   </si>
   <si>
-    <t>角色2</t>
+    <t>小女孩</t>
   </si>
   <si>
-    <t>角色3</t>
+    <t>股市大亨</t>
   </si>
   <si>
-    <t>角色4</t>
+    <t>棒球学长</t>
   </si>
   <si>
-    <t>角色5</t>
+    <t>基金经理</t>
   </si>
   <si>
-    <t>角色6</t>
+    <t>列车乘务</t>
   </si>
   <si>
-    <t>角色7</t>
+    <t>健身教练</t>
   </si>
 </sst>
 </file>
@@ -1251,10 +1251,11 @@
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1272,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>70</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1332,10 +1333,10 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="1">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:7">

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -94,10 +94,10 @@
     <t>小女孩</t>
   </si>
   <si>
-    <t>股市大亨</t>
+    <t>棒球学长</t>
   </si>
   <si>
-    <t>棒球学长</t>
+    <t>股市大亨</t>
   </si>
   <si>
     <t>基金经理</t>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>18</v>
@@ -1234,9 +1234,6 @@
       </c>
       <c r="E6" s="1">
         <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1253,42 +1250,44 @@
       <c r="E7" s="1">
         <v>3</v>
       </c>
-      <c r="F7" s="1"/>
       <c r="G7" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="1">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="1">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:7">

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -94,19 +94,19 @@
     <t>小女孩</t>
   </si>
   <si>
-    <t>棒球学长</t>
+    <t>股市大亨</t>
   </si>
   <si>
-    <t>股市大亨</t>
+    <t>健身教练</t>
+  </si>
+  <si>
+    <t>棒球学长</t>
   </si>
   <si>
     <t>基金经理</t>
   </si>
   <si>
     <t>列车乘务</t>
-  </si>
-  <si>
-    <t>健身教练</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6" s="4">
         <v>3</v>
@@ -1256,28 +1256,28 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>21</v>
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1295,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>22</v>
@@ -1310,7 +1310,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>23</v>
@@ -1325,17 +1325,14 @@
         <v>7</v>
       </c>
       <c r="B12" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>500</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game002\cocosProject\LieFlatGame\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game002\cocosProject\LieFlatGame\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:7">

--- a/excel/roleSkin.xlsx
+++ b/excel/roleSkin.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game002\cocosProject\LieFlatGame\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game002\cocosProject\LieFlatGame\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -114,19 +114,19 @@
     <t>列车乘务</t>
   </si>
   <si>
-    <t>丧尸1</t>
+    <t>卡恩・腐脊</t>
   </si>
   <si>
-    <t>丧尸0</t>
+    <t>尸瑰罗西</t>
   </si>
   <si>
-    <t>丧尸2</t>
+    <t>布丽安娜</t>
   </si>
   <si>
-    <t>丧尸3</t>
+    <t>血骸巨汉</t>
   </si>
   <si>
-    <t>丧尸4</t>
+    <t>腐骸狱卫</t>
   </si>
 </sst>
 </file>
